--- a/Data/2022_F013B4_CO_ISSWC/2022_F013B4_CO_ISSWC_SoilAnalysis.xlsx
+++ b/Data/2022_F013B4_CO_ISSWC/2022_F013B4_CO_ISSWC_SoilAnalysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2022_F013B4_CO_ISSWC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D9A94F-61F8-45F7-89AB-BFD8DF55961C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6785FA-A936-489F-8F92-E06319810A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16500" yWindow="-21090" windowWidth="17805" windowHeight="20370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1881,6 +1881,9 @@
       <c r="A3">
         <v>2022</v>
       </c>
+      <c r="B3">
+        <v>108</v>
+      </c>
       <c r="C3" t="s">
         <v>269</v>
       </c>
@@ -1896,13 +1899,13 @@
       <c r="G3" s="3">
         <v>0.66</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="6">
         <v>1.4</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="6">
         <v>8.1</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="6">
         <v>10</v>
       </c>
       <c r="K3" s="7">
@@ -1940,6 +1943,9 @@
       <c r="A4">
         <v>2022</v>
       </c>
+      <c r="B4">
+        <v>108</v>
+      </c>
       <c r="C4" t="s">
         <v>269</v>
       </c>
@@ -1955,13 +1961,13 @@
       <c r="G4" s="3">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="6">
         <v>0.8</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="6">
         <v>23.7</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="6">
         <v>8.3000000000000007</v>
       </c>
       <c r="K4" s="7">
@@ -1999,6 +2005,9 @@
       <c r="A5">
         <v>2022</v>
       </c>
+      <c r="B5">
+        <v>108</v>
+      </c>
       <c r="C5" t="s">
         <v>269</v>
       </c>
@@ -2014,13 +2023,13 @@
       <c r="G5" s="3">
         <v>2.04</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="6">
         <v>0.9</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="6">
         <v>13.2</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="6">
         <v>56.9</v>
       </c>
       <c r="K5" s="7">
@@ -2058,6 +2067,9 @@
       <c r="A6">
         <v>2022</v>
       </c>
+      <c r="B6">
+        <v>108</v>
+      </c>
       <c r="C6" t="s">
         <v>269</v>
       </c>
@@ -2073,13 +2085,13 @@
       <c r="G6" s="3">
         <v>1.22</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="6">
         <v>0.8</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="6">
         <v>5.8</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="6">
         <v>7.5</v>
       </c>
       <c r="K6" s="7">
@@ -2117,6 +2129,9 @@
       <c r="A7">
         <v>2022</v>
       </c>
+      <c r="B7">
+        <v>108</v>
+      </c>
       <c r="C7" t="s">
         <v>269</v>
       </c>
@@ -2132,13 +2147,13 @@
       <c r="G7" s="3">
         <v>0.8</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="6">
         <v>0.8</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="6">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="6">
         <v>7.9</v>
       </c>
       <c r="K7" s="7">
@@ -2176,6 +2191,9 @@
       <c r="A8">
         <v>2022</v>
       </c>
+      <c r="B8">
+        <v>108</v>
+      </c>
       <c r="C8" t="s">
         <v>270</v>
       </c>
@@ -2191,13 +2209,13 @@
       <c r="G8" s="3">
         <v>0.89</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="6">
         <v>1.4</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="6">
         <v>8.9</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="6">
         <v>9.4</v>
       </c>
       <c r="K8" s="7">
@@ -2235,6 +2253,9 @@
       <c r="A9">
         <v>2022</v>
       </c>
+      <c r="B9">
+        <v>108</v>
+      </c>
       <c r="C9" t="s">
         <v>270</v>
       </c>
@@ -2250,13 +2271,13 @@
       <c r="G9" s="3">
         <v>1.41</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="6">
         <v>0.9</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="6">
         <v>5.3</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="6">
         <v>8.4</v>
       </c>
       <c r="K9" s="7">
@@ -2294,6 +2315,9 @@
       <c r="A10">
         <v>2022</v>
       </c>
+      <c r="B10">
+        <v>108</v>
+      </c>
       <c r="C10" t="s">
         <v>270</v>
       </c>
@@ -2309,13 +2333,13 @@
       <c r="G10" s="3">
         <v>1.31</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="6">
         <v>1</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="6">
         <v>9.1999999999999993</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="6">
         <v>8.3000000000000007</v>
       </c>
       <c r="K10" s="7">
@@ -2353,6 +2377,9 @@
       <c r="A11">
         <v>2022</v>
       </c>
+      <c r="B11">
+        <v>108</v>
+      </c>
       <c r="C11" t="s">
         <v>270</v>
       </c>
@@ -2368,13 +2395,13 @@
       <c r="G11" s="3">
         <v>0.47</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="6">
         <v>0.6</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="6">
         <v>1.5</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="6">
         <v>8.4</v>
       </c>
       <c r="K11" s="7">
@@ -2412,6 +2439,9 @@
       <c r="A12">
         <v>2022</v>
       </c>
+      <c r="B12">
+        <v>108</v>
+      </c>
       <c r="C12" t="s">
         <v>270</v>
       </c>
@@ -2427,13 +2457,13 @@
       <c r="G12" s="3">
         <v>0.85</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="6">
         <v>0.8</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="6">
         <v>3.3</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="6">
         <v>8.1999999999999993</v>
       </c>
       <c r="K12" s="7">
@@ -2471,6 +2501,9 @@
       <c r="A13">
         <v>2022</v>
       </c>
+      <c r="B13">
+        <v>108</v>
+      </c>
       <c r="C13" t="s">
         <v>271</v>
       </c>
@@ -2486,13 +2519,13 @@
       <c r="G13" s="3">
         <v>0.91</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="6">
         <v>1.3</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="6">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="6">
         <v>9.9</v>
       </c>
       <c r="K13" s="7">
@@ -2530,6 +2563,9 @@
       <c r="A14">
         <v>2022</v>
       </c>
+      <c r="B14">
+        <v>108</v>
+      </c>
       <c r="C14" t="s">
         <v>271</v>
       </c>
@@ -2545,13 +2581,13 @@
       <c r="G14" s="3">
         <v>0.87</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="6">
         <v>0.8</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="6">
         <v>5.2</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="6">
         <v>8.1</v>
       </c>
       <c r="K14" s="7">
@@ -2589,6 +2625,9 @@
       <c r="A15">
         <v>2022</v>
       </c>
+      <c r="B15">
+        <v>108</v>
+      </c>
       <c r="C15" t="s">
         <v>271</v>
       </c>
@@ -2604,13 +2643,13 @@
       <c r="G15" s="3">
         <v>0.8</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="6">
         <v>0.6</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="6">
         <v>5</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="6">
         <v>6.5</v>
       </c>
       <c r="K15" s="7">
@@ -2648,6 +2687,9 @@
       <c r="A16">
         <v>2022</v>
       </c>
+      <c r="B16">
+        <v>108</v>
+      </c>
       <c r="C16" t="s">
         <v>271</v>
       </c>
@@ -2663,13 +2705,13 @@
       <c r="G16" s="3">
         <v>1.2</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="6">
         <v>0.9</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="6">
         <v>6.3</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="6">
         <v>7.8</v>
       </c>
       <c r="K16" s="7">
@@ -2707,6 +2749,9 @@
       <c r="A17">
         <v>2022</v>
       </c>
+      <c r="B17">
+        <v>108</v>
+      </c>
       <c r="C17" t="s">
         <v>271</v>
       </c>
@@ -2722,13 +2767,13 @@
       <c r="G17" s="3">
         <v>0.78</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="6">
         <v>0.7</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="6">
         <v>2.8</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="6">
         <v>8.1999999999999993</v>
       </c>
       <c r="K17" s="7">
@@ -2766,6 +2811,9 @@
       <c r="A18">
         <v>2022</v>
       </c>
+      <c r="B18">
+        <v>108</v>
+      </c>
       <c r="C18" t="s">
         <v>272</v>
       </c>
@@ -2781,13 +2829,13 @@
       <c r="G18" s="3">
         <v>0.54</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="6">
         <v>1.4</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="6">
         <v>8.9</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="6">
         <v>8.9</v>
       </c>
       <c r="K18" s="7">
@@ -2825,6 +2873,9 @@
       <c r="A19">
         <v>2022</v>
       </c>
+      <c r="B19">
+        <v>108</v>
+      </c>
       <c r="C19" t="s">
         <v>272</v>
       </c>
@@ -2840,13 +2891,13 @@
       <c r="G19" s="3">
         <v>0.77</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="6">
         <v>0.8</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="6">
         <v>5.5</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="6">
         <v>8.4</v>
       </c>
       <c r="K19" s="7">
@@ -2884,6 +2935,9 @@
       <c r="A20">
         <v>2022</v>
       </c>
+      <c r="B20">
+        <v>108</v>
+      </c>
       <c r="C20" t="s">
         <v>272</v>
       </c>
@@ -2899,13 +2953,13 @@
       <c r="G20" s="3">
         <v>2.42</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="6">
         <v>0.9</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="6">
         <v>5.6</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="6">
         <v>8.1999999999999993</v>
       </c>
       <c r="K20" s="7">
@@ -2943,6 +2997,9 @@
       <c r="A21">
         <v>2022</v>
       </c>
+      <c r="B21">
+        <v>108</v>
+      </c>
       <c r="C21" t="s">
         <v>272</v>
       </c>
@@ -2958,13 +3015,13 @@
       <c r="G21" s="3">
         <v>1.1200000000000001</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="6">
         <v>0.8</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="6">
         <v>8.5</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="6">
         <v>7.9</v>
       </c>
       <c r="K21" s="7">
@@ -3002,6 +3059,9 @@
       <c r="A22">
         <v>2022</v>
       </c>
+      <c r="B22">
+        <v>108</v>
+      </c>
       <c r="C22" t="s">
         <v>272</v>
       </c>
@@ -3017,13 +3077,13 @@
       <c r="G22" s="3">
         <v>0.7</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="6">
         <v>0.8</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="6">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="6">
         <v>8</v>
       </c>
       <c r="K22" s="7">
@@ -3061,6 +3121,9 @@
       <c r="A23">
         <v>2022</v>
       </c>
+      <c r="B23">
+        <v>108</v>
+      </c>
       <c r="C23" t="s">
         <v>273</v>
       </c>
@@ -3076,13 +3139,13 @@
       <c r="G23" s="3">
         <v>0.61</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="6">
         <v>1.4</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="6">
         <v>3.1</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="6">
         <v>9.1</v>
       </c>
       <c r="K23" s="7">
@@ -3120,6 +3183,9 @@
       <c r="A24">
         <v>2022</v>
       </c>
+      <c r="B24">
+        <v>108</v>
+      </c>
       <c r="C24" t="s">
         <v>273</v>
       </c>
@@ -3135,13 +3201,13 @@
       <c r="G24" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="6">
         <v>0.8</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="6">
         <v>2.7</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="6">
         <v>8</v>
       </c>
       <c r="K24" s="7">
@@ -3179,6 +3245,9 @@
       <c r="A25">
         <v>2022</v>
       </c>
+      <c r="B25">
+        <v>108</v>
+      </c>
       <c r="C25" t="s">
         <v>273</v>
       </c>
@@ -3194,13 +3263,13 @@
       <c r="G25" s="3">
         <v>2.04</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="6">
         <v>0.9</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="6">
         <v>4.2</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="6">
         <v>8.1</v>
       </c>
       <c r="K25" s="7">
@@ -3238,6 +3307,9 @@
       <c r="A26">
         <v>2022</v>
       </c>
+      <c r="B26">
+        <v>108</v>
+      </c>
       <c r="C26" t="s">
         <v>273</v>
       </c>
@@ -3253,13 +3325,13 @@
       <c r="G26" s="3">
         <v>1.21</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="6">
         <v>1</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="6">
         <v>2.7</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="6">
         <v>8.1</v>
       </c>
       <c r="K26" s="7">
@@ -3297,6 +3369,9 @@
       <c r="A27">
         <v>2022</v>
       </c>
+      <c r="B27">
+        <v>108</v>
+      </c>
       <c r="C27" t="s">
         <v>273</v>
       </c>
@@ -3312,13 +3387,13 @@
       <c r="G27" s="3">
         <v>0.96</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="6">
         <v>1</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="6">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="6">
         <v>8.4</v>
       </c>
       <c r="K27" s="7">
@@ -3356,6 +3431,9 @@
       <c r="A28">
         <v>2022</v>
       </c>
+      <c r="B28">
+        <v>108</v>
+      </c>
       <c r="C28" t="s">
         <v>274</v>
       </c>
@@ -3371,13 +3449,13 @@
       <c r="G28" s="3">
         <v>0.49</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="6">
         <v>1.3</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="6">
         <v>7.7</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="6">
         <v>8.6999999999999993</v>
       </c>
       <c r="K28" s="7">
@@ -3415,6 +3493,9 @@
       <c r="A29">
         <v>2022</v>
       </c>
+      <c r="B29">
+        <v>108</v>
+      </c>
       <c r="C29" t="s">
         <v>274</v>
       </c>
@@ -3430,13 +3511,13 @@
       <c r="G29" s="3">
         <v>0.72</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="6">
         <v>0.9</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="6">
         <v>2.8</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="6">
         <v>8</v>
       </c>
       <c r="K29" s="7">
@@ -3474,6 +3555,9 @@
       <c r="A30">
         <v>2022</v>
       </c>
+      <c r="B30">
+        <v>108</v>
+      </c>
       <c r="C30" t="s">
         <v>274</v>
       </c>
@@ -3489,13 +3573,13 @@
       <c r="G30" s="3">
         <v>0.86</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="6">
         <v>0.8</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="6">
         <v>6</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="6">
         <v>8</v>
       </c>
       <c r="K30" s="7">
@@ -3533,6 +3617,9 @@
       <c r="A31">
         <v>2022</v>
       </c>
+      <c r="B31">
+        <v>108</v>
+      </c>
       <c r="C31" t="s">
         <v>274</v>
       </c>
@@ -3548,13 +3635,13 @@
       <c r="G31" s="3">
         <v>1.1499999999999999</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="6">
         <v>0.7</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="6">
         <v>9.1</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="6">
         <v>8.1999999999999993</v>
       </c>
       <c r="K31" s="7">
@@ -3592,6 +3679,9 @@
       <c r="A32">
         <v>2022</v>
       </c>
+      <c r="B32">
+        <v>108</v>
+      </c>
       <c r="C32" t="s">
         <v>274</v>
       </c>
@@ -3607,13 +3697,13 @@
       <c r="G32" s="3">
         <v>1.45</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="6">
         <v>0.9</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="6">
         <v>6.3</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="6">
         <v>8</v>
       </c>
       <c r="K32" s="7">

--- a/Data/2022_F013B4_CO_ISSWC/2022_F013B4_CO_ISSWC_SoilAnalysis.xlsx
+++ b/Data/2022_F013B4_CO_ISSWC/2022_F013B4_CO_ISSWC_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2022_F013B4_CO_ISSWC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6785FA-A936-489F-8F92-E06319810A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4049BC-6B11-4746-9704-586C016E2292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16500" yWindow="-21090" windowWidth="17805" windowHeight="20370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16545" yWindow="-21345" windowWidth="17805" windowHeight="20370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDF" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="292">
   <si>
     <t>Kind Of Sample</t>
   </si>
@@ -905,15 +905,19 @@
   </si>
   <si>
     <t>SLCEC</t>
+  </si>
+  <si>
+    <t>SOIL_DATE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -1398,7 +1402,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1407,6 +1411,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1762,60 +1767,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{806945E5-8549-44EC-9B0A-34CFC97C5A04}">
-  <dimension ref="A1:T32"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="E1" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>28</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>29</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>30</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>31</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>32</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>34</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>35</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>36</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>265</v>
       </c>
@@ -1823,1917 +1831,2010 @@
         <v>266</v>
       </c>
       <c r="C2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D2" t="s">
         <v>267</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>268</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>275</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>276</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>277</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>278</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>279</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>280</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>281</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>282</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>283</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>284</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>285</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>286</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>287</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>288</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>289</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2022</v>
       </c>
       <c r="B3">
         <v>108</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D3" t="s">
         <v>269</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>20</v>
       </c>
-      <c r="E3" s="6">
+      <c r="F3" s="6">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F3" s="6">
+      <c r="G3" s="6">
         <v>7.2</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="3">
         <v>0.66</v>
       </c>
-      <c r="H3" s="6">
+      <c r="I3" s="6">
         <v>1.4</v>
       </c>
-      <c r="I3" s="6">
+      <c r="J3" s="6">
         <v>8.1</v>
       </c>
-      <c r="J3" s="6">
+      <c r="K3" s="6">
         <v>10</v>
       </c>
-      <c r="K3" s="7">
+      <c r="L3" s="7">
         <v>347</v>
       </c>
-      <c r="L3" s="6">
+      <c r="M3" s="6">
         <v>90</v>
       </c>
-      <c r="M3" s="3">
+      <c r="N3" s="3">
         <v>1.68</v>
       </c>
-      <c r="N3" s="6">
+      <c r="O3" s="6">
         <v>9.1</v>
       </c>
-      <c r="O3" s="6">
+      <c r="P3" s="6">
         <v>14.7</v>
       </c>
-      <c r="P3" s="3">
+      <c r="Q3" s="3">
         <v>3.53</v>
       </c>
-      <c r="Q3" s="7">
+      <c r="R3" s="7">
         <v>2570</v>
       </c>
-      <c r="R3" s="7">
+      <c r="S3" s="7">
         <v>219</v>
       </c>
-      <c r="S3" s="7">
+      <c r="T3" s="7">
         <v>474</v>
       </c>
-      <c r="T3" s="6">
+      <c r="U3" s="6">
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2022</v>
       </c>
       <c r="B4">
         <v>108</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D4" t="s">
         <v>269</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>60</v>
       </c>
-      <c r="E4" s="6">
+      <c r="F4" s="6">
         <v>8.1</v>
       </c>
-      <c r="F4" s="6">
+      <c r="G4" s="6">
         <v>7.2</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H4" s="6">
+      <c r="I4" s="6">
         <v>0.8</v>
       </c>
-      <c r="I4" s="6">
+      <c r="J4" s="6">
         <v>23.7</v>
       </c>
-      <c r="J4" s="6">
+      <c r="K4" s="6">
         <v>8.3000000000000007</v>
       </c>
-      <c r="K4" s="7">
+      <c r="L4" s="7">
         <v>172</v>
       </c>
-      <c r="L4" s="6">
+      <c r="M4" s="6">
         <v>424.4</v>
       </c>
-      <c r="M4" s="3">
+      <c r="N4" s="3">
         <v>0.68</v>
       </c>
-      <c r="N4" s="6">
+      <c r="O4" s="6">
         <v>6.8</v>
       </c>
-      <c r="O4" s="6">
+      <c r="P4" s="6">
         <v>6.7</v>
       </c>
-      <c r="P4" s="3">
+      <c r="Q4" s="3">
         <v>2.06</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="R4" s="7">
         <v>4111</v>
       </c>
-      <c r="R4" s="7">
+      <c r="S4" s="7">
         <v>282</v>
       </c>
-      <c r="S4" s="7">
+      <c r="T4" s="7">
         <v>891</v>
       </c>
-      <c r="T4" s="6">
+      <c r="U4" s="6">
         <v>27.2</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2022</v>
       </c>
       <c r="B5">
         <v>108</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D5" t="s">
         <v>269</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>100</v>
       </c>
-      <c r="E5" s="6">
+      <c r="F5" s="6">
         <v>8</v>
       </c>
-      <c r="F5" s="6">
+      <c r="G5" s="6">
         <v>7.2</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>2.04</v>
       </c>
-      <c r="H5" s="6">
+      <c r="I5" s="6">
         <v>0.9</v>
       </c>
-      <c r="I5" s="6">
+      <c r="J5" s="6">
         <v>13.2</v>
       </c>
-      <c r="J5" s="6">
+      <c r="K5" s="6">
         <v>56.9</v>
       </c>
-      <c r="K5" s="7">
+      <c r="L5" s="7">
         <v>88</v>
       </c>
-      <c r="L5" s="6">
+      <c r="M5" s="6">
         <v>401.5</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>0.4</v>
       </c>
-      <c r="N5" s="6">
+      <c r="O5" s="6">
         <v>4.5999999999999996</v>
       </c>
-      <c r="O5" s="6">
+      <c r="P5" s="6">
         <v>3</v>
       </c>
-      <c r="P5" s="3">
+      <c r="Q5" s="3">
         <v>0.83</v>
       </c>
-      <c r="Q5" s="7">
+      <c r="R5" s="7">
         <v>4098</v>
       </c>
-      <c r="R5" s="7">
+      <c r="S5" s="7">
         <v>252</v>
       </c>
-      <c r="S5" s="7">
+      <c r="T5" s="7">
         <v>624</v>
       </c>
-      <c r="T5" s="6">
+      <c r="U5" s="6">
         <v>25.5</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2022</v>
       </c>
       <c r="B6">
         <v>108</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D6" t="s">
         <v>269</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>140</v>
       </c>
-      <c r="E6" s="6">
+      <c r="F6" s="6">
         <v>8.1</v>
       </c>
-      <c r="F6" s="6">
+      <c r="G6" s="6">
         <v>7.2</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>1.22</v>
       </c>
-      <c r="H6" s="6">
+      <c r="I6" s="6">
         <v>0.8</v>
       </c>
-      <c r="I6" s="6">
+      <c r="J6" s="6">
         <v>5.8</v>
       </c>
-      <c r="J6" s="6">
+      <c r="K6" s="6">
         <v>7.5</v>
       </c>
-      <c r="K6" s="7">
+      <c r="L6" s="7">
         <v>85</v>
       </c>
-      <c r="L6" s="6">
+      <c r="M6" s="6">
         <v>102.6</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>0.46</v>
       </c>
-      <c r="N6" s="6">
+      <c r="O6" s="6">
         <v>3.7</v>
       </c>
-      <c r="O6" s="6">
+      <c r="P6" s="6">
         <v>2</v>
       </c>
-      <c r="P6" s="3">
+      <c r="Q6" s="3">
         <v>0.48</v>
       </c>
-      <c r="Q6" s="7">
+      <c r="R6" s="7">
         <v>3888</v>
       </c>
-      <c r="R6" s="7">
+      <c r="S6" s="7">
         <v>238</v>
       </c>
-      <c r="S6" s="7">
+      <c r="T6" s="7">
         <v>397</v>
       </c>
-      <c r="T6" s="6">
+      <c r="U6" s="6">
         <v>23.4</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2022</v>
       </c>
       <c r="B7">
         <v>108</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D7" t="s">
         <v>269</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>180</v>
       </c>
-      <c r="E7" s="6">
+      <c r="F7" s="6">
         <v>8.1</v>
       </c>
-      <c r="F7" s="6">
+      <c r="G7" s="6">
         <v>7.2</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>0.8</v>
       </c>
-      <c r="H7" s="6">
+      <c r="I7" s="6">
         <v>0.8</v>
       </c>
-      <c r="I7" s="6">
+      <c r="J7" s="6">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J7" s="6">
+      <c r="K7" s="6">
         <v>7.9</v>
       </c>
-      <c r="K7" s="7">
+      <c r="L7" s="7">
         <v>84</v>
       </c>
-      <c r="L7" s="6">
+      <c r="M7" s="6">
         <v>75</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>0.73</v>
       </c>
-      <c r="N7" s="6">
+      <c r="O7" s="6">
         <v>5.0999999999999996</v>
       </c>
-      <c r="O7" s="6">
+      <c r="P7" s="6">
         <v>3</v>
       </c>
-      <c r="P7" s="3">
+      <c r="Q7" s="3">
         <v>0.56999999999999995</v>
       </c>
-      <c r="Q7" s="7">
+      <c r="R7" s="7">
         <v>3377</v>
       </c>
-      <c r="R7" s="7">
+      <c r="S7" s="7">
         <v>207</v>
       </c>
-      <c r="S7" s="7">
+      <c r="T7" s="7">
         <v>284</v>
       </c>
-      <c r="T7" s="6">
+      <c r="U7" s="6">
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2022</v>
       </c>
       <c r="B8">
         <v>108</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D8" t="s">
         <v>270</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>20</v>
       </c>
-      <c r="E8" s="6">
+      <c r="F8" s="6">
         <v>8.1</v>
       </c>
-      <c r="F8" s="6">
+      <c r="G8" s="6">
         <v>7.2</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>0.89</v>
       </c>
-      <c r="H8" s="6">
+      <c r="I8" s="6">
         <v>1.4</v>
       </c>
-      <c r="I8" s="6">
+      <c r="J8" s="6">
         <v>8.9</v>
       </c>
-      <c r="J8" s="6">
+      <c r="K8" s="6">
         <v>9.4</v>
       </c>
-      <c r="K8" s="7">
+      <c r="L8" s="7">
         <v>283</v>
       </c>
-      <c r="L8" s="6">
+      <c r="M8" s="6">
         <v>126.4</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1.61</v>
       </c>
-      <c r="N8" s="6">
+      <c r="O8" s="6">
         <v>10.199999999999999</v>
       </c>
-      <c r="O8" s="6">
+      <c r="P8" s="6">
         <v>14.6</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3.49</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="R8" s="7">
         <v>2322</v>
       </c>
-      <c r="R8" s="7">
+      <c r="S8" s="7">
         <v>209</v>
       </c>
-      <c r="S8" s="7">
+      <c r="T8" s="7">
         <v>419</v>
       </c>
-      <c r="T8" s="6">
+      <c r="U8" s="6">
         <v>15.9</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2022</v>
       </c>
       <c r="B9">
         <v>108</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D9" t="s">
         <v>270</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>60</v>
       </c>
-      <c r="E9" s="6">
+      <c r="F9" s="6">
         <v>8</v>
       </c>
-      <c r="F9" s="6">
+      <c r="G9" s="6">
         <v>7.2</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1.41</v>
       </c>
-      <c r="H9" s="6">
+      <c r="I9" s="6">
         <v>0.9</v>
       </c>
-      <c r="I9" s="6">
+      <c r="J9" s="6">
         <v>5.3</v>
       </c>
-      <c r="J9" s="6">
+      <c r="K9" s="6">
         <v>8.4</v>
       </c>
-      <c r="K9" s="7">
+      <c r="L9" s="7">
         <v>216</v>
       </c>
-      <c r="L9" s="6">
+      <c r="M9" s="6">
         <v>269</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>0.54</v>
       </c>
-      <c r="N9" s="6">
+      <c r="O9" s="6">
         <v>7.6</v>
       </c>
-      <c r="O9" s="6">
+      <c r="P9" s="6">
         <v>8.5</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2.14</v>
       </c>
-      <c r="Q9" s="7">
+      <c r="R9" s="7">
         <v>3562</v>
       </c>
-      <c r="R9" s="7">
+      <c r="S9" s="7">
         <v>309</v>
       </c>
-      <c r="S9" s="7">
+      <c r="T9" s="7">
         <v>775</v>
       </c>
-      <c r="T9" s="6">
+      <c r="U9" s="6">
         <v>24.3</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2022</v>
       </c>
       <c r="B10">
         <v>108</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D10" t="s">
         <v>270</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>100</v>
       </c>
-      <c r="E10" s="6">
+      <c r="F10" s="6">
         <v>8.1</v>
       </c>
-      <c r="F10" s="6">
+      <c r="G10" s="6">
         <v>7.2</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1.31</v>
       </c>
-      <c r="H10" s="6">
+      <c r="I10" s="6">
         <v>1</v>
       </c>
-      <c r="I10" s="6">
+      <c r="J10" s="6">
         <v>9.1999999999999993</v>
       </c>
-      <c r="J10" s="6">
+      <c r="K10" s="6">
         <v>8.3000000000000007</v>
       </c>
-      <c r="K10" s="7">
+      <c r="L10" s="7">
         <v>138</v>
       </c>
-      <c r="L10" s="6">
+      <c r="M10" s="6">
         <v>277.39999999999998</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>0.31</v>
       </c>
-      <c r="N10" s="6">
+      <c r="O10" s="6">
         <v>6.6</v>
       </c>
-      <c r="O10" s="6">
+      <c r="P10" s="6">
         <v>5.0999999999999996</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1.2</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="R10" s="7">
         <v>4384</v>
       </c>
-      <c r="R10" s="7">
+      <c r="S10" s="7">
         <v>302</v>
       </c>
-      <c r="S10" s="7">
+      <c r="T10" s="7">
         <v>737</v>
       </c>
-      <c r="T10" s="6">
+      <c r="U10" s="6">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2022</v>
       </c>
       <c r="B11">
         <v>108</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D11" t="s">
         <v>270</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>140</v>
       </c>
-      <c r="E11" s="6">
+      <c r="F11" s="6">
         <v>8.4</v>
       </c>
-      <c r="F11" s="6">
+      <c r="G11" s="6">
         <v>7.2</v>
       </c>
-      <c r="G11" s="3">
+      <c r="H11" s="3">
         <v>0.47</v>
       </c>
-      <c r="H11" s="6">
+      <c r="I11" s="6">
         <v>0.6</v>
       </c>
-      <c r="I11" s="6">
+      <c r="J11" s="6">
         <v>1.5</v>
       </c>
-      <c r="J11" s="6">
+      <c r="K11" s="6">
         <v>8.4</v>
       </c>
-      <c r="K11" s="7">
+      <c r="L11" s="7">
         <v>84</v>
       </c>
-      <c r="L11" s="6">
+      <c r="M11" s="6">
         <v>36.4</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="3">
         <v>0.45</v>
       </c>
-      <c r="N11" s="6">
+      <c r="O11" s="6">
         <v>5.4</v>
       </c>
-      <c r="O11" s="6">
+      <c r="P11" s="6">
         <v>3.1</v>
       </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="3">
         <v>0.66</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="R11" s="7">
         <v>3375</v>
       </c>
-      <c r="R11" s="7">
+      <c r="S11" s="7">
         <v>186</v>
       </c>
-      <c r="S11" s="7">
+      <c r="T11" s="7">
         <v>273</v>
       </c>
-      <c r="T11" s="6">
+      <c r="U11" s="6">
         <v>19.8</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2022</v>
       </c>
       <c r="B12">
         <v>108</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D12" t="s">
         <v>270</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>180</v>
       </c>
-      <c r="E12" s="6">
+      <c r="F12" s="6">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F12" s="6">
+      <c r="G12" s="6">
         <v>7.2</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>0.85</v>
       </c>
-      <c r="H12" s="6">
+      <c r="I12" s="6">
         <v>0.8</v>
       </c>
-      <c r="I12" s="6">
+      <c r="J12" s="6">
         <v>3.3</v>
       </c>
-      <c r="J12" s="6">
+      <c r="K12" s="6">
         <v>8.1999999999999993</v>
       </c>
-      <c r="K12" s="7">
+      <c r="L12" s="7">
         <v>126</v>
       </c>
-      <c r="L12" s="6">
+      <c r="M12" s="6">
         <v>76.599999999999994</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>0.32</v>
       </c>
-      <c r="N12" s="6">
+      <c r="O12" s="6">
         <v>5.4</v>
       </c>
-      <c r="O12" s="6">
+      <c r="P12" s="6">
         <v>3.5</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>0.7</v>
       </c>
-      <c r="Q12" s="7">
+      <c r="R12" s="7">
         <v>3966</v>
       </c>
-      <c r="R12" s="7">
+      <c r="S12" s="7">
         <v>278</v>
       </c>
-      <c r="S12" s="7">
+      <c r="T12" s="7">
         <v>506</v>
       </c>
-      <c r="T12" s="6">
+      <c r="U12" s="6">
         <v>24.7</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2022</v>
       </c>
       <c r="B13">
         <v>108</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D13" t="s">
         <v>271</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>20</v>
       </c>
-      <c r="E13" s="6">
+      <c r="F13" s="6">
         <v>8.1</v>
       </c>
-      <c r="F13" s="6">
+      <c r="G13" s="6">
         <v>7.2</v>
       </c>
-      <c r="G13" s="3">
+      <c r="H13" s="3">
         <v>0.91</v>
       </c>
-      <c r="H13" s="6">
+      <c r="I13" s="6">
         <v>1.3</v>
       </c>
-      <c r="I13" s="6">
+      <c r="J13" s="6">
         <v>4.0999999999999996</v>
       </c>
-      <c r="J13" s="6">
+      <c r="K13" s="6">
         <v>9.9</v>
       </c>
-      <c r="K13" s="7">
+      <c r="L13" s="7">
         <v>354</v>
       </c>
-      <c r="L13" s="6">
+      <c r="M13" s="6">
         <v>161.30000000000001</v>
       </c>
-      <c r="M13" s="3">
+      <c r="N13" s="3">
         <v>1.81</v>
       </c>
-      <c r="N13" s="6">
+      <c r="O13" s="6">
         <v>8.6</v>
       </c>
-      <c r="O13" s="6">
+      <c r="P13" s="6">
         <v>15</v>
       </c>
-      <c r="P13" s="3">
+      <c r="Q13" s="3">
         <v>3.2</v>
       </c>
-      <c r="Q13" s="7">
+      <c r="R13" s="7">
         <v>2649</v>
       </c>
-      <c r="R13" s="7">
+      <c r="S13" s="7">
         <v>239</v>
       </c>
-      <c r="S13" s="7">
+      <c r="T13" s="7">
         <v>552</v>
       </c>
-      <c r="T13" s="6">
+      <c r="U13" s="6">
         <v>18.5</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2022</v>
       </c>
       <c r="B14">
         <v>108</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D14" t="s">
         <v>271</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>60</v>
       </c>
-      <c r="E14" s="6">
+      <c r="F14" s="6">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F14" s="6">
+      <c r="G14" s="6">
         <v>7.2</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>0.87</v>
       </c>
-      <c r="H14" s="6">
+      <c r="I14" s="6">
         <v>0.8</v>
       </c>
-      <c r="I14" s="6">
+      <c r="J14" s="6">
         <v>5.2</v>
       </c>
-      <c r="J14" s="6">
+      <c r="K14" s="6">
         <v>8.1</v>
       </c>
-      <c r="K14" s="7">
+      <c r="L14" s="7">
         <v>190</v>
       </c>
-      <c r="L14" s="6">
+      <c r="M14" s="6">
         <v>98</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>0.78</v>
       </c>
-      <c r="N14" s="6">
+      <c r="O14" s="6">
         <v>7.6</v>
       </c>
-      <c r="O14" s="6">
+      <c r="P14" s="6">
         <v>8.6</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1.76</v>
       </c>
-      <c r="Q14" s="7">
+      <c r="R14" s="7">
         <v>3219</v>
       </c>
-      <c r="R14" s="7">
+      <c r="S14" s="7">
         <v>212</v>
       </c>
-      <c r="S14" s="7">
+      <c r="T14" s="7">
         <v>548</v>
       </c>
-      <c r="T14" s="6">
+      <c r="U14" s="6">
         <v>20.7</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2022</v>
       </c>
       <c r="B15">
         <v>108</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D15" t="s">
         <v>271</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>100</v>
       </c>
-      <c r="E15" s="6">
+      <c r="F15" s="6">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F15" s="6">
+      <c r="G15" s="6">
         <v>7.2</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>0.8</v>
       </c>
-      <c r="H15" s="6">
+      <c r="I15" s="6">
         <v>0.6</v>
       </c>
-      <c r="I15" s="6">
+      <c r="J15" s="6">
         <v>5</v>
       </c>
-      <c r="J15" s="6">
+      <c r="K15" s="6">
         <v>6.5</v>
       </c>
-      <c r="K15" s="7">
+      <c r="L15" s="7">
         <v>176</v>
       </c>
-      <c r="L15" s="6">
+      <c r="M15" s="6">
         <v>100.1</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>0.54</v>
       </c>
-      <c r="N15" s="6">
+      <c r="O15" s="6">
         <v>6.3</v>
       </c>
-      <c r="O15" s="6">
+      <c r="P15" s="6">
         <v>6.7</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1.34</v>
       </c>
-      <c r="Q15" s="7">
+      <c r="R15" s="7">
         <v>3470</v>
       </c>
-      <c r="R15" s="7">
+      <c r="S15" s="7">
         <v>222</v>
       </c>
-      <c r="S15" s="7">
+      <c r="T15" s="7">
         <v>476</v>
       </c>
-      <c r="T15" s="6">
+      <c r="U15" s="6">
         <v>21.7</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2022</v>
       </c>
       <c r="B16">
         <v>108</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D16" t="s">
         <v>271</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>140</v>
       </c>
-      <c r="E16" s="6">
+      <c r="F16" s="6">
         <v>8.1</v>
       </c>
-      <c r="F16" s="6">
+      <c r="G16" s="6">
         <v>7.2</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>1.2</v>
       </c>
-      <c r="H16" s="6">
+      <c r="I16" s="6">
         <v>0.9</v>
       </c>
-      <c r="I16" s="6">
+      <c r="J16" s="6">
         <v>6.3</v>
       </c>
-      <c r="J16" s="6">
+      <c r="K16" s="6">
         <v>7.8</v>
       </c>
-      <c r="K16" s="7">
+      <c r="L16" s="7">
         <v>141</v>
       </c>
-      <c r="L16" s="6">
+      <c r="M16" s="6">
         <v>294.8</v>
       </c>
-      <c r="M16" s="3">
+      <c r="N16" s="3">
         <v>0.37</v>
       </c>
-      <c r="N16" s="6">
+      <c r="O16" s="6">
         <v>6.1</v>
       </c>
-      <c r="O16" s="6">
+      <c r="P16" s="6">
         <v>4.4000000000000004</v>
       </c>
-      <c r="P16" s="3">
+      <c r="Q16" s="3">
         <v>0.8</v>
       </c>
-      <c r="Q16" s="7">
+      <c r="R16" s="7">
         <v>4028</v>
       </c>
-      <c r="R16" s="7">
+      <c r="S16" s="7">
         <v>284</v>
       </c>
-      <c r="S16" s="7">
+      <c r="T16" s="7">
         <v>480</v>
       </c>
-      <c r="T16" s="6">
+      <c r="U16" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2022</v>
       </c>
       <c r="B17">
         <v>108</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D17" t="s">
         <v>271</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>180</v>
       </c>
-      <c r="E17" s="6">
+      <c r="F17" s="6">
         <v>8.1</v>
       </c>
-      <c r="F17" s="6">
+      <c r="G17" s="6">
         <v>7.2</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>0.78</v>
       </c>
-      <c r="H17" s="6">
+      <c r="I17" s="6">
         <v>0.7</v>
       </c>
-      <c r="I17" s="6">
+      <c r="J17" s="6">
         <v>2.8</v>
       </c>
-      <c r="J17" s="6">
+      <c r="K17" s="6">
         <v>8.1999999999999993</v>
       </c>
-      <c r="K17" s="7">
+      <c r="L17" s="7">
         <v>85</v>
       </c>
-      <c r="L17" s="6">
+      <c r="M17" s="6">
         <v>112.7</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>0.33</v>
       </c>
-      <c r="N17" s="6">
+      <c r="O17" s="6">
         <v>4.8</v>
       </c>
-      <c r="O17" s="6">
+      <c r="P17" s="6">
         <v>2.6</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>0.48</v>
       </c>
-      <c r="Q17" s="7">
+      <c r="R17" s="7">
         <v>3550</v>
       </c>
-      <c r="R17" s="7">
+      <c r="S17" s="7">
         <v>197</v>
       </c>
-      <c r="S17" s="7">
+      <c r="T17" s="7">
         <v>256</v>
       </c>
-      <c r="T17" s="6">
+      <c r="U17" s="6">
         <v>20.7</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2022</v>
       </c>
       <c r="B18">
         <v>108</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D18" t="s">
         <v>272</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>20</v>
       </c>
-      <c r="E18" s="6">
+      <c r="F18" s="6">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F18" s="6">
+      <c r="G18" s="6">
         <v>7.2</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>0.54</v>
       </c>
-      <c r="H18" s="6">
+      <c r="I18" s="6">
         <v>1.4</v>
-      </c>
-      <c r="I18" s="6">
-        <v>8.9</v>
       </c>
       <c r="J18" s="6">
         <v>8.9</v>
       </c>
-      <c r="K18" s="7">
+      <c r="K18" s="6">
+        <v>8.9</v>
+      </c>
+      <c r="L18" s="7">
         <v>277</v>
       </c>
-      <c r="L18" s="6">
+      <c r="M18" s="6">
         <v>63.2</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1.63</v>
       </c>
-      <c r="N18" s="6">
+      <c r="O18" s="6">
         <v>8</v>
       </c>
-      <c r="O18" s="6">
+      <c r="P18" s="6">
         <v>15.9</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3.37</v>
       </c>
-      <c r="Q18" s="7">
+      <c r="R18" s="7">
         <v>2178</v>
       </c>
-      <c r="R18" s="7">
+      <c r="S18" s="7">
         <v>205</v>
       </c>
-      <c r="S18" s="7">
+      <c r="T18" s="7">
         <v>298</v>
       </c>
-      <c r="T18" s="6">
+      <c r="U18" s="6">
         <v>14.6</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2022</v>
       </c>
       <c r="B19">
         <v>108</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D19" t="s">
         <v>272</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>60</v>
       </c>
-      <c r="E19" s="6">
+      <c r="F19" s="6">
         <v>8.5</v>
       </c>
-      <c r="F19" s="6">
+      <c r="G19" s="6">
         <v>7.2</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="3">
         <v>0.77</v>
       </c>
-      <c r="H19" s="6">
+      <c r="I19" s="6">
         <v>0.8</v>
       </c>
-      <c r="I19" s="6">
+      <c r="J19" s="6">
         <v>5.5</v>
       </c>
-      <c r="J19" s="6">
+      <c r="K19" s="6">
         <v>8.4</v>
       </c>
-      <c r="K19" s="7">
+      <c r="L19" s="7">
         <v>166</v>
       </c>
-      <c r="L19" s="6">
+      <c r="M19" s="6">
         <v>119</v>
       </c>
-      <c r="M19" s="3">
+      <c r="N19" s="3">
         <v>0.81</v>
       </c>
-      <c r="N19" s="6">
+      <c r="O19" s="6">
         <v>7.4</v>
       </c>
-      <c r="O19" s="6">
+      <c r="P19" s="6">
         <v>8.9</v>
       </c>
-      <c r="P19" s="3">
+      <c r="Q19" s="3">
         <v>2.2200000000000002</v>
       </c>
-      <c r="Q19" s="7">
+      <c r="R19" s="7">
         <v>3600</v>
       </c>
-      <c r="R19" s="7">
+      <c r="S19" s="7">
         <v>228</v>
       </c>
-      <c r="S19" s="7">
+      <c r="T19" s="7">
         <v>608</v>
       </c>
-      <c r="T19" s="6">
+      <c r="U19" s="6">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2022</v>
       </c>
       <c r="B20">
         <v>108</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D20" t="s">
         <v>272</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>100</v>
       </c>
-      <c r="E20" s="6">
+      <c r="F20" s="6">
         <v>8.1</v>
       </c>
-      <c r="F20" s="6">
+      <c r="G20" s="6">
         <v>7.2</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2.42</v>
       </c>
-      <c r="H20" s="6">
+      <c r="I20" s="6">
         <v>0.9</v>
       </c>
-      <c r="I20" s="6">
+      <c r="J20" s="6">
         <v>5.6</v>
       </c>
-      <c r="J20" s="6">
+      <c r="K20" s="6">
         <v>8.1999999999999993</v>
       </c>
-      <c r="K20" s="7">
+      <c r="L20" s="7">
         <v>120</v>
       </c>
-      <c r="L20" s="6">
+      <c r="M20" s="6">
         <v>368.4</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>0.31</v>
       </c>
-      <c r="N20" s="6">
+      <c r="O20" s="6">
         <v>5.9</v>
       </c>
-      <c r="O20" s="6">
+      <c r="P20" s="6">
         <v>3.9</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>0.99</v>
       </c>
-      <c r="Q20" s="7">
+      <c r="R20" s="7">
         <v>4093</v>
       </c>
-      <c r="R20" s="7">
+      <c r="S20" s="7">
         <v>313</v>
       </c>
-      <c r="S20" s="7">
+      <c r="T20" s="7">
         <v>742</v>
       </c>
-      <c r="T20" s="6">
+      <c r="U20" s="6">
         <v>26.6</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2022</v>
       </c>
       <c r="B21">
         <v>108</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D21" t="s">
         <v>272</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>140</v>
       </c>
-      <c r="E21" s="6">
+      <c r="F21" s="6">
         <v>8</v>
       </c>
-      <c r="F21" s="6">
+      <c r="G21" s="6">
         <v>7.2</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1.1200000000000001</v>
       </c>
-      <c r="H21" s="6">
+      <c r="I21" s="6">
         <v>0.8</v>
       </c>
-      <c r="I21" s="6">
+      <c r="J21" s="6">
         <v>8.5</v>
       </c>
-      <c r="J21" s="6">
+      <c r="K21" s="6">
         <v>7.9</v>
       </c>
-      <c r="K21" s="7">
+      <c r="L21" s="7">
         <v>112</v>
       </c>
-      <c r="L21" s="6">
+      <c r="M21" s="6">
         <v>149.1</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>0.48</v>
       </c>
-      <c r="N21" s="6">
+      <c r="O21" s="6">
         <v>5.9</v>
       </c>
-      <c r="O21" s="6">
+      <c r="P21" s="6">
         <v>4.8</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>0.94</v>
       </c>
-      <c r="Q21" s="7">
+      <c r="R21" s="7">
         <v>3603</v>
       </c>
-      <c r="R21" s="7">
+      <c r="S21" s="7">
         <v>238</v>
       </c>
-      <c r="S21" s="7">
+      <c r="T21" s="7">
         <v>363</v>
       </c>
-      <c r="T21" s="6">
+      <c r="U21" s="6">
         <v>21.9</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2022</v>
       </c>
       <c r="B22">
         <v>108</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D22" t="s">
         <v>272</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>180</v>
       </c>
-      <c r="E22" s="6">
+      <c r="F22" s="6">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F22" s="6">
+      <c r="G22" s="6">
         <v>7.2</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>0.7</v>
       </c>
-      <c r="H22" s="6">
+      <c r="I22" s="6">
         <v>0.8</v>
       </c>
-      <c r="I22" s="6">
+      <c r="J22" s="6">
         <v>4.9000000000000004</v>
       </c>
-      <c r="J22" s="6">
+      <c r="K22" s="6">
         <v>8</v>
       </c>
-      <c r="K22" s="7">
+      <c r="L22" s="7">
         <v>90</v>
       </c>
-      <c r="L22" s="6">
+      <c r="M22" s="6">
         <v>71.7</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>0.36</v>
       </c>
-      <c r="N22" s="6">
+      <c r="O22" s="6">
         <v>5.0999999999999996</v>
       </c>
-      <c r="O22" s="6">
+      <c r="P22" s="6">
         <v>3.4</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>0.73</v>
       </c>
-      <c r="Q22" s="7">
+      <c r="R22" s="7">
         <v>3448</v>
       </c>
-      <c r="R22" s="7">
+      <c r="S22" s="7">
         <v>202</v>
       </c>
-      <c r="S22" s="7">
+      <c r="T22" s="7">
         <v>240</v>
       </c>
-      <c r="T22" s="6">
+      <c r="U22" s="6">
         <v>20.2</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2022</v>
       </c>
       <c r="B23">
         <v>108</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D23" t="s">
         <v>273</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>20</v>
       </c>
-      <c r="E23" s="6">
+      <c r="F23" s="6">
         <v>8.1</v>
       </c>
-      <c r="F23" s="6">
+      <c r="G23" s="6">
         <v>7.2</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>0.61</v>
       </c>
-      <c r="H23" s="6">
+      <c r="I23" s="6">
         <v>1.4</v>
       </c>
-      <c r="I23" s="6">
+      <c r="J23" s="6">
         <v>3.1</v>
       </c>
-      <c r="J23" s="6">
+      <c r="K23" s="6">
         <v>9.1</v>
       </c>
-      <c r="K23" s="7">
+      <c r="L23" s="7">
         <v>287</v>
       </c>
-      <c r="L23" s="6">
+      <c r="M23" s="6">
         <v>81.599999999999994</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1.43</v>
       </c>
-      <c r="N23" s="6">
+      <c r="O23" s="6">
         <v>8.3000000000000007</v>
       </c>
-      <c r="O23" s="6">
+      <c r="P23" s="6">
         <v>13.6</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2.93</v>
       </c>
-      <c r="Q23" s="7">
+      <c r="R23" s="7">
         <v>1964</v>
       </c>
-      <c r="R23" s="7">
+      <c r="S23" s="7">
         <v>209</v>
       </c>
-      <c r="S23" s="7">
+      <c r="T23" s="7">
         <v>393</v>
       </c>
-      <c r="T23" s="6">
+      <c r="U23" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2022</v>
       </c>
       <c r="B24">
         <v>108</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D24" t="s">
         <v>273</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>60</v>
       </c>
-      <c r="E24" s="6">
+      <c r="F24" s="6">
         <v>8.1999999999999993</v>
       </c>
-      <c r="F24" s="6">
+      <c r="G24" s="6">
         <v>7.2</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H24" s="6">
+      <c r="I24" s="6">
         <v>0.8</v>
       </c>
-      <c r="I24" s="6">
+      <c r="J24" s="6">
         <v>2.7</v>
       </c>
-      <c r="J24" s="6">
+      <c r="K24" s="6">
         <v>8</v>
       </c>
-      <c r="K24" s="7">
+      <c r="L24" s="7">
         <v>152</v>
       </c>
-      <c r="L24" s="6">
+      <c r="M24" s="6">
         <v>162.1</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>0.4</v>
       </c>
-      <c r="N24" s="6">
+      <c r="O24" s="6">
         <v>7.8</v>
       </c>
-      <c r="O24" s="6">
+      <c r="P24" s="6">
         <v>6.9</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1.73</v>
       </c>
-      <c r="Q24" s="7">
+      <c r="R24" s="7">
         <v>2985</v>
       </c>
-      <c r="R24" s="7">
+      <c r="S24" s="7">
         <v>237</v>
       </c>
-      <c r="S24" s="7">
+      <c r="T24" s="7">
         <v>675</v>
       </c>
-      <c r="T24" s="6">
+      <c r="U24" s="6">
         <v>20.2</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2022</v>
       </c>
       <c r="B25">
         <v>108</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D25" t="s">
         <v>273</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>100</v>
       </c>
-      <c r="E25" s="6">
+      <c r="F25" s="6">
         <v>8.1</v>
       </c>
-      <c r="F25" s="6">
+      <c r="G25" s="6">
         <v>7.2</v>
       </c>
-      <c r="G25" s="3">
+      <c r="H25" s="3">
         <v>2.04</v>
       </c>
-      <c r="H25" s="6">
+      <c r="I25" s="6">
         <v>0.9</v>
       </c>
-      <c r="I25" s="6">
+      <c r="J25" s="6">
         <v>4.2</v>
       </c>
-      <c r="J25" s="6">
+      <c r="K25" s="6">
         <v>8.1</v>
       </c>
-      <c r="K25" s="7">
+      <c r="L25" s="7">
         <v>136</v>
       </c>
-      <c r="L25" s="6">
+      <c r="M25" s="6">
         <v>183.7</v>
       </c>
-      <c r="M25" s="3">
+      <c r="N25" s="3">
         <v>0.42</v>
       </c>
-      <c r="N25" s="6">
+      <c r="O25" s="6">
         <v>6.5</v>
       </c>
-      <c r="O25" s="6">
+      <c r="P25" s="6">
         <v>5.8</v>
       </c>
-      <c r="P25" s="3">
+      <c r="Q25" s="3">
         <v>1.04</v>
       </c>
-      <c r="Q25" s="7">
+      <c r="R25" s="7">
         <v>3909</v>
       </c>
-      <c r="R25" s="7">
+      <c r="S25" s="7">
         <v>255</v>
       </c>
-      <c r="S25" s="7">
+      <c r="T25" s="7">
         <v>637</v>
       </c>
-      <c r="T25" s="6">
+      <c r="U25" s="6">
         <v>24.8</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2022</v>
       </c>
       <c r="B26">
         <v>108</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D26" t="s">
         <v>273</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>140</v>
       </c>
-      <c r="E26" s="6">
+      <c r="F26" s="6">
         <v>8.1</v>
       </c>
-      <c r="F26" s="6">
+      <c r="G26" s="6">
         <v>7.2</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1.21</v>
       </c>
-      <c r="H26" s="6">
+      <c r="I26" s="6">
         <v>1</v>
       </c>
-      <c r="I26" s="6">
+      <c r="J26" s="6">
         <v>2.7</v>
       </c>
-      <c r="J26" s="6">
+      <c r="K26" s="6">
         <v>8.1</v>
       </c>
-      <c r="K26" s="7">
+      <c r="L26" s="7">
         <v>129</v>
       </c>
-      <c r="L26" s="6">
+      <c r="M26" s="6">
         <v>229.9</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>0.35</v>
       </c>
-      <c r="N26" s="6">
+      <c r="O26" s="6">
         <v>9.5</v>
       </c>
-      <c r="O26" s="6">
+      <c r="P26" s="6">
         <v>3.7</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>0.77</v>
       </c>
-      <c r="Q26" s="7">
+      <c r="R26" s="7">
         <v>3955</v>
       </c>
-      <c r="R26" s="7">
+      <c r="S26" s="7">
         <v>282</v>
       </c>
-      <c r="S26" s="7">
+      <c r="T26" s="7">
         <v>456</v>
       </c>
-      <c r="T26" s="6">
+      <c r="U26" s="6">
         <v>24.4</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2022</v>
       </c>
       <c r="B27">
         <v>108</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D27" t="s">
         <v>273</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>180</v>
       </c>
-      <c r="E27" s="6">
+      <c r="F27" s="6">
         <v>8.1</v>
       </c>
-      <c r="F27" s="6">
+      <c r="G27" s="6">
         <v>7.2</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>0.96</v>
       </c>
-      <c r="H27" s="6">
+      <c r="I27" s="6">
         <v>1</v>
       </c>
-      <c r="I27" s="6">
+      <c r="J27" s="6">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J27" s="6">
+      <c r="K27" s="6">
         <v>8.4</v>
       </c>
-      <c r="K27" s="7">
+      <c r="L27" s="7">
         <v>111</v>
       </c>
-      <c r="L27" s="6">
+      <c r="M27" s="6">
         <v>130.6</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>0.48</v>
-      </c>
-      <c r="N27" s="6">
-        <v>6.2</v>
       </c>
       <c r="O27" s="6">
         <v>6.2</v>
       </c>
-      <c r="P27" s="3">
+      <c r="P27" s="6">
+        <v>6.2</v>
+      </c>
+      <c r="Q27" s="3">
         <v>0.88</v>
       </c>
-      <c r="Q27" s="7">
+      <c r="R27" s="7">
         <v>3702</v>
       </c>
-      <c r="R27" s="7">
+      <c r="S27" s="7">
         <v>257</v>
       </c>
-      <c r="S27" s="7">
+      <c r="T27" s="7">
         <v>302</v>
       </c>
-      <c r="T27" s="6">
+      <c r="U27" s="6">
         <v>22.2</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2022</v>
       </c>
       <c r="B28">
         <v>108</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D28" t="s">
         <v>274</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>20</v>
       </c>
-      <c r="E28" s="6">
+      <c r="F28" s="6">
         <v>8.3000000000000007</v>
       </c>
-      <c r="F28" s="6">
+      <c r="G28" s="6">
         <v>7.2</v>
       </c>
-      <c r="G28" s="3">
+      <c r="H28" s="3">
         <v>0.49</v>
       </c>
-      <c r="H28" s="6">
+      <c r="I28" s="6">
         <v>1.3</v>
       </c>
-      <c r="I28" s="6">
+      <c r="J28" s="6">
         <v>7.7</v>
       </c>
-      <c r="J28" s="6">
+      <c r="K28" s="6">
         <v>8.6999999999999993</v>
       </c>
-      <c r="K28" s="7">
+      <c r="L28" s="7">
         <v>220</v>
       </c>
-      <c r="L28" s="6">
+      <c r="M28" s="6">
         <v>35.4</v>
       </c>
-      <c r="M28" s="3">
+      <c r="N28" s="3">
         <v>1.2</v>
       </c>
-      <c r="N28" s="6">
+      <c r="O28" s="6">
         <v>7.8</v>
       </c>
-      <c r="O28" s="6">
+      <c r="P28" s="6">
         <v>15.5</v>
       </c>
-      <c r="P28" s="3">
+      <c r="Q28" s="3">
         <v>3.02</v>
       </c>
-      <c r="Q28" s="7">
+      <c r="R28" s="7">
         <v>2352</v>
       </c>
-      <c r="R28" s="7">
+      <c r="S28" s="7">
         <v>179</v>
       </c>
-      <c r="S28" s="7">
+      <c r="T28" s="7">
         <v>220</v>
       </c>
-      <c r="T28" s="6">
+      <c r="U28" s="6">
         <v>14.8</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2022</v>
       </c>
       <c r="B29">
         <v>108</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D29" t="s">
         <v>274</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>60</v>
       </c>
-      <c r="E29" s="6">
+      <c r="F29" s="6">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F29" s="6">
+      <c r="G29" s="6">
         <v>7.2</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>0.72</v>
       </c>
-      <c r="H29" s="6">
+      <c r="I29" s="6">
         <v>0.9</v>
       </c>
-      <c r="I29" s="6">
+      <c r="J29" s="6">
         <v>2.8</v>
       </c>
-      <c r="J29" s="6">
+      <c r="K29" s="6">
         <v>8</v>
       </c>
-      <c r="K29" s="7">
+      <c r="L29" s="7">
         <v>99</v>
       </c>
-      <c r="L29" s="6">
+      <c r="M29" s="6">
         <v>43</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>0.4</v>
       </c>
-      <c r="N29" s="6">
+      <c r="O29" s="6">
         <v>6.5</v>
       </c>
-      <c r="O29" s="6">
+      <c r="P29" s="6">
         <v>5.2</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>1.43</v>
       </c>
-      <c r="Q29" s="7">
+      <c r="R29" s="7">
         <v>3517</v>
       </c>
-      <c r="R29" s="7">
+      <c r="S29" s="7">
         <v>195</v>
       </c>
-      <c r="S29" s="7">
+      <c r="T29" s="7">
         <v>461</v>
       </c>
-      <c r="T29" s="6">
+      <c r="U29" s="6">
         <v>21.5</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2022</v>
       </c>
       <c r="B30">
         <v>108</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D30" t="s">
         <v>274</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>100</v>
       </c>
-      <c r="E30" s="6">
+      <c r="F30" s="6">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F30" s="6">
+      <c r="G30" s="6">
         <v>7.2</v>
       </c>
-      <c r="G30" s="3">
+      <c r="H30" s="3">
         <v>0.86</v>
       </c>
-      <c r="H30" s="6">
+      <c r="I30" s="6">
         <v>0.8</v>
       </c>
-      <c r="I30" s="6">
+      <c r="J30" s="6">
         <v>6</v>
       </c>
-      <c r="J30" s="6">
+      <c r="K30" s="6">
         <v>8</v>
       </c>
-      <c r="K30" s="7">
+      <c r="L30" s="7">
         <v>85</v>
       </c>
-      <c r="L30" s="6">
+      <c r="M30" s="6">
         <v>91.3</v>
       </c>
-      <c r="M30" s="3">
+      <c r="N30" s="3">
         <v>0.3</v>
       </c>
-      <c r="N30" s="6">
+      <c r="O30" s="6">
         <v>5.2</v>
       </c>
-      <c r="O30" s="6">
+      <c r="P30" s="6">
         <v>3.2</v>
       </c>
-      <c r="P30" s="3">
+      <c r="Q30" s="3">
         <v>0.67</v>
       </c>
-      <c r="Q30" s="7">
+      <c r="R30" s="7">
         <v>3517</v>
       </c>
-      <c r="R30" s="7">
+      <c r="S30" s="7">
         <v>186</v>
       </c>
-      <c r="S30" s="7">
+      <c r="T30" s="7">
         <v>469</v>
       </c>
-      <c r="T30" s="6">
+      <c r="U30" s="6">
         <v>21.4</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2022</v>
       </c>
       <c r="B31">
         <v>108</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D31" t="s">
         <v>274</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>140</v>
       </c>
-      <c r="E31" s="6">
+      <c r="F31" s="6">
         <v>8.4</v>
       </c>
-      <c r="F31" s="6">
+      <c r="G31" s="6">
         <v>7.2</v>
       </c>
-      <c r="G31" s="3">
+      <c r="H31" s="3">
         <v>1.1499999999999999</v>
       </c>
-      <c r="H31" s="6">
+      <c r="I31" s="6">
         <v>0.7</v>
       </c>
-      <c r="I31" s="6">
+      <c r="J31" s="6">
         <v>9.1</v>
       </c>
-      <c r="J31" s="6">
+      <c r="K31" s="6">
         <v>8.1999999999999993</v>
       </c>
-      <c r="K31" s="7">
+      <c r="L31" s="7">
         <v>79</v>
       </c>
-      <c r="L31" s="6">
+      <c r="M31" s="6">
         <v>172.6</v>
       </c>
-      <c r="M31" s="3">
+      <c r="N31" s="3">
         <v>0.16</v>
       </c>
-      <c r="N31" s="6">
+      <c r="O31" s="6">
         <v>4.0999999999999996</v>
       </c>
-      <c r="O31" s="6">
+      <c r="P31" s="6">
         <v>1.9</v>
       </c>
-      <c r="P31" s="3">
+      <c r="Q31" s="3">
         <v>0.36</v>
       </c>
-      <c r="Q31" s="7">
+      <c r="R31" s="7">
         <v>3667</v>
       </c>
-      <c r="R31" s="7">
+      <c r="S31" s="7">
         <v>221</v>
       </c>
-      <c r="S31" s="7">
+      <c r="T31" s="7">
         <v>434</v>
       </c>
-      <c r="T31" s="6">
+      <c r="U31" s="6">
         <v>22.3</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2022</v>
       </c>
       <c r="B32">
         <v>108</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="8">
+        <v>44669</v>
+      </c>
+      <c r="D32" t="s">
         <v>274</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>180</v>
       </c>
-      <c r="E32" s="6">
+      <c r="F32" s="6">
         <v>8.1</v>
       </c>
-      <c r="F32" s="6">
+      <c r="G32" s="6">
         <v>7.2</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1.45</v>
       </c>
-      <c r="H32" s="6">
+      <c r="I32" s="6">
         <v>0.9</v>
       </c>
-      <c r="I32" s="6">
+      <c r="J32" s="6">
         <v>6.3</v>
       </c>
-      <c r="J32" s="6">
+      <c r="K32" s="6">
         <v>8</v>
       </c>
-      <c r="K32" s="7">
+      <c r="L32" s="7">
         <v>70</v>
       </c>
-      <c r="L32" s="6">
+      <c r="M32" s="6">
         <v>168.6</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>0.28999999999999998</v>
       </c>
-      <c r="N32" s="6">
+      <c r="O32" s="6">
         <v>5.0999999999999996</v>
       </c>
-      <c r="O32" s="6">
+      <c r="P32" s="6">
         <v>2.9</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>0.46</v>
       </c>
-      <c r="Q32" s="7">
+      <c r="R32" s="7">
         <v>3620</v>
       </c>
-      <c r="R32" s="7">
+      <c r="S32" s="7">
         <v>205</v>
       </c>
-      <c r="S32" s="7">
+      <c r="T32" s="7">
         <v>287</v>
       </c>
-      <c r="T32" s="6">
+      <c r="U32" s="6">
         <v>21.2</v>
       </c>
     </row>

--- a/Data/2022_F013B4_CO_ISSWC/2022_F013B4_CO_ISSWC_SoilAnalysis.xlsx
+++ b/Data/2022_F013B4_CO_ISSWC/2022_F013B4_CO_ISSWC_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2022_F013B4_CO_ISSWC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CC7473-5165-440B-AD1B-2AF4E365F8C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F09993-6E37-474C-97AB-93656B2CE857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16320" yWindow="-28050" windowWidth="17910" windowHeight="25080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1665" yWindow="-24510" windowWidth="27270" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="5" r:id="rId1"/>
@@ -1053,9 +1053,6 @@
     <t>p01-1</t>
   </si>
   <si>
-    <t>2013d260EM38</t>
-  </si>
-  <si>
     <t>2015d118EM38</t>
   </si>
   <si>
@@ -1627,6 +1624,9 @@
   </si>
   <si>
     <t>2016-p16-1</t>
+  </si>
+  <si>
+    <t>2013d260EM38V</t>
   </si>
 </sst>
 </file>
@@ -2475,13 +2475,13 @@
         <v>296</v>
       </c>
       <c r="B1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -2492,7 +2492,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C2">
         <v>408706.2476</v>
@@ -2509,7 +2509,7 @@
         <v>116</v>
       </c>
       <c r="B3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C3">
         <v>408705.94109999901</v>
@@ -2526,7 +2526,7 @@
         <v>129</v>
       </c>
       <c r="B4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C4">
         <v>408699.85230000003</v>
@@ -2543,7 +2543,7 @@
         <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C5">
         <v>408700.13030000002</v>
@@ -2560,7 +2560,7 @@
         <v>117</v>
       </c>
       <c r="B6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C6">
         <v>408705.62539999897</v>
@@ -2577,7 +2577,7 @@
         <v>118</v>
       </c>
       <c r="B7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C7">
         <v>408705.38500000001</v>
@@ -2594,7 +2594,7 @@
         <v>127</v>
       </c>
       <c r="B8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C8">
         <v>408699.26530000003</v>
@@ -2611,7 +2611,7 @@
         <v>128</v>
       </c>
       <c r="B9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C9">
         <v>408699.535299999</v>
@@ -2628,7 +2628,7 @@
         <v>119</v>
       </c>
       <c r="B10" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C10">
         <v>408704.99829999899</v>
@@ -2645,7 +2645,7 @@
         <v>126</v>
       </c>
       <c r="B11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C11">
         <v>408698.93699999899</v>
@@ -2662,7 +2662,7 @@
         <v>121</v>
       </c>
       <c r="B12" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C12">
         <v>408704.38349999901</v>
@@ -2679,7 +2679,7 @@
         <v>124</v>
       </c>
       <c r="B13" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C13">
         <v>408698.26829999901</v>
@@ -2696,7 +2696,7 @@
         <v>99</v>
       </c>
       <c r="B14" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C14">
         <v>408720.46580000001</v>
@@ -2713,7 +2713,7 @@
         <v>100</v>
       </c>
       <c r="B15" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C15">
         <v>408720.19679999899</v>
@@ -2730,7 +2730,7 @@
         <v>113</v>
       </c>
       <c r="B16" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C16">
         <v>408714.09700000001</v>
@@ -2747,7 +2747,7 @@
         <v>114</v>
       </c>
       <c r="B17" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C17">
         <v>408714.40309999901</v>
@@ -2764,7 +2764,7 @@
         <v>101</v>
       </c>
       <c r="B18" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C18">
         <v>408719.8885</v>
@@ -2781,7 +2781,7 @@
         <v>102</v>
       </c>
       <c r="B19" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C19">
         <v>408719.60830000002</v>
@@ -2798,7 +2798,7 @@
         <v>111</v>
       </c>
       <c r="B20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C20">
         <v>408713.53340000001</v>
@@ -2815,7 +2815,7 @@
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C21">
         <v>408713.790299999</v>
@@ -2832,7 +2832,7 @@
         <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C22">
         <v>408719.22999999899</v>
@@ -2849,7 +2849,7 @@
         <v>110</v>
       </c>
       <c r="B23" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C23">
         <v>408713.13880000002</v>
@@ -2866,7 +2866,7 @@
         <v>105</v>
       </c>
       <c r="B24" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C24">
         <v>408718.61729999899</v>
@@ -2883,7 +2883,7 @@
         <v>108</v>
       </c>
       <c r="B25" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C25">
         <v>408712.455599999</v>
@@ -2900,7 +2900,7 @@
         <v>83</v>
       </c>
       <c r="B26" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C26">
         <v>408734.69020000001</v>
@@ -2917,7 +2917,7 @@
         <v>84</v>
       </c>
       <c r="B27" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C27">
         <v>408734.44760000001</v>
@@ -2934,7 +2934,7 @@
         <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C28">
         <v>408728.347899999</v>
@@ -2951,7 +2951,7 @@
         <v>98</v>
       </c>
       <c r="B29" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C29">
         <v>408728.57990000001</v>
@@ -2968,7 +2968,7 @@
         <v>85</v>
       </c>
       <c r="B30" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C30">
         <v>408734.16200000001</v>
@@ -2985,7 +2985,7 @@
         <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C31">
         <v>408733.81439999898</v>
@@ -3002,7 +3002,7 @@
         <v>95</v>
       </c>
       <c r="B32" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C32">
         <v>408727.74089999998</v>
@@ -3019,7 +3019,7 @@
         <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C33">
         <v>408727.98920000001</v>
@@ -3036,7 +3036,7 @@
         <v>87</v>
       </c>
       <c r="B34" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C34">
         <v>408733.443499999</v>
@@ -3053,7 +3053,7 @@
         <v>94</v>
       </c>
       <c r="B35" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C35">
         <v>408727.3763</v>
@@ -3070,7 +3070,7 @@
         <v>89</v>
       </c>
       <c r="B36" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C36">
         <v>408732.84250000003</v>
@@ -3087,7 +3087,7 @@
         <v>92</v>
       </c>
       <c r="B37" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C37">
         <v>408726.75140000001</v>
@@ -3104,7 +3104,7 @@
         <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C38">
         <v>408748.9094</v>
@@ -3121,7 +3121,7 @@
         <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C39">
         <v>408748.6594</v>
@@ -3138,7 +3138,7 @@
         <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C40">
         <v>408742.57679999899</v>
@@ -3155,7 +3155,7 @@
         <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C41">
         <v>408742.84710000001</v>
@@ -3172,7 +3172,7 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C42">
         <v>408748.33390000003</v>
@@ -3189,7 +3189,7 @@
         <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C43">
         <v>408747.98800000001</v>
@@ -3206,7 +3206,7 @@
         <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C44">
         <v>408741.9215</v>
@@ -3223,7 +3223,7 @@
         <v>80</v>
       </c>
       <c r="B45" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C45">
         <v>408742.204399999</v>
@@ -3240,7 +3240,7 @@
         <v>71</v>
       </c>
       <c r="B46" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C46">
         <v>408747.652899999</v>
@@ -3257,7 +3257,7 @@
         <v>78</v>
       </c>
       <c r="B47" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C47">
         <v>408741.583099999</v>
@@ -3274,7 +3274,7 @@
         <v>73</v>
       </c>
       <c r="B48" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C48">
         <v>408747.01990000001</v>
@@ -3291,7 +3291,7 @@
         <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C49">
         <v>408740.96580000001</v>
@@ -3308,7 +3308,7 @@
         <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C50">
         <v>408760.11839999899</v>
@@ -3325,7 +3325,7 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C51">
         <v>408759.24219999899</v>
@@ -3342,7 +3342,7 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C52">
         <v>408758.807399999</v>
@@ -3359,7 +3359,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C53">
         <v>408758.367499999</v>
@@ -3376,7 +3376,7 @@
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C54">
         <v>408788.581799999</v>
@@ -3393,7 +3393,7 @@
         <v>166</v>
       </c>
       <c r="B55" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C55">
         <v>408793.35800000001</v>
@@ -3410,7 +3410,7 @@
         <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C56">
         <v>408787.67560000002</v>
@@ -3427,7 +3427,7 @@
         <v>167</v>
       </c>
       <c r="B57" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C57">
         <v>408792.866099999</v>
@@ -3444,7 +3444,7 @@
         <v>52</v>
       </c>
       <c r="B58" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C58">
         <v>408787.222799999</v>
@@ -3461,7 +3461,7 @@
         <v>168</v>
       </c>
       <c r="B59" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C59">
         <v>408792.38530000002</v>
@@ -3478,7 +3478,7 @@
         <v>53</v>
       </c>
       <c r="B60" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C60">
         <v>408786.80749999901</v>
@@ -3495,7 +3495,7 @@
         <v>170</v>
       </c>
       <c r="B61" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C61">
         <v>408791.43050000002</v>
@@ -3512,7 +3512,7 @@
         <v>48</v>
       </c>
       <c r="B62" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C62">
         <v>408817.00829999999</v>
@@ -3529,7 +3529,7 @@
         <v>46</v>
       </c>
       <c r="B63" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C63">
         <v>408816.12689999898</v>
@@ -3546,7 +3546,7 @@
         <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C64">
         <v>408815.666399999</v>
@@ -3563,7 +3563,7 @@
         <v>44</v>
       </c>
       <c r="B65" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C65">
         <v>408815.248499999</v>
@@ -3580,7 +3580,7 @@
         <v>37</v>
       </c>
       <c r="B66" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C66">
         <v>408845.46089999902</v>
@@ -3597,7 +3597,7 @@
         <v>156</v>
       </c>
       <c r="B67" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C67">
         <v>408850.18070000003</v>
@@ -3614,7 +3614,7 @@
         <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C68">
         <v>408844.56319999899</v>
@@ -3631,7 +3631,7 @@
         <v>157</v>
       </c>
       <c r="B69" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C69">
         <v>408849.70020000002</v>
@@ -3648,7 +3648,7 @@
         <v>40</v>
       </c>
       <c r="B70" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C70">
         <v>408844.13500000001</v>
@@ -3665,7 +3665,7 @@
         <v>158</v>
       </c>
       <c r="B71" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C71">
         <v>408849.219199999</v>
@@ -3682,7 +3682,7 @@
         <v>41</v>
       </c>
       <c r="B72" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C72">
         <v>408843.68329999998</v>
@@ -3699,7 +3699,7 @@
         <v>160</v>
       </c>
       <c r="B73" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C73">
         <v>408848.231299999</v>
@@ -3729,13 +3729,13 @@
         <v>296</v>
       </c>
       <c r="B1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -3746,7 +3746,7 @@
         <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C2">
         <v>408702.95299999899</v>
@@ -3763,7 +3763,7 @@
         <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C3">
         <v>408702.35950000002</v>
@@ -3780,7 +3780,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C4">
         <v>408701.76500000001</v>
@@ -3797,7 +3797,7 @@
         <v>64</v>
       </c>
       <c r="B5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C5">
         <v>408701.14669999899</v>
@@ -3814,7 +3814,7 @@
         <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C6">
         <v>408717.2047</v>
@@ -3831,7 +3831,7 @@
         <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C7">
         <v>408716.59240000002</v>
@@ -3848,7 +3848,7 @@
         <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C8">
         <v>408715.98029999901</v>
@@ -3865,7 +3865,7 @@
         <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C9">
         <v>408715.38030000002</v>
@@ -3882,7 +3882,7 @@
         <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C10">
         <v>408731.41739999899</v>
@@ -3899,7 +3899,7 @@
         <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C11">
         <v>408730.80660000001</v>
@@ -3916,7 +3916,7 @@
         <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C12">
         <v>408730.19</v>
@@ -3933,7 +3933,7 @@
         <v>56</v>
       </c>
       <c r="B13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C13">
         <v>408729.61050000001</v>
@@ -3950,7 +3950,7 @@
         <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C14">
         <v>408745.63719999901</v>
@@ -3967,7 +3967,7 @@
         <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C15">
         <v>408745.02610000002</v>
@@ -3984,7 +3984,7 @@
         <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C16">
         <v>408744.41419999901</v>
@@ -4001,7 +4001,7 @@
         <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C17">
         <v>408743.81449999899</v>
@@ -4018,7 +4018,7 @@
         <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C18">
         <v>408759.7758</v>
@@ -4035,7 +4035,7 @@
         <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C19">
         <v>408759.1692</v>
@@ -4052,7 +4052,7 @@
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C20">
         <v>408758.57179999899</v>
@@ -4069,7 +4069,7 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C21">
         <v>408757.959299999</v>
@@ -4086,7 +4086,7 @@
         <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C22">
         <v>408773.99790000002</v>
@@ -4103,7 +4103,7 @@
         <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C23">
         <v>408773.39649999898</v>
@@ -4120,7 +4120,7 @@
         <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C24">
         <v>408772.784099999</v>
@@ -4137,7 +4137,7 @@
         <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C25">
         <v>408772.17050000001</v>
@@ -4154,7 +4154,7 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C26">
         <v>408788.22350000002</v>
@@ -4171,7 +4171,7 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C27">
         <v>408787.60700000002</v>
@@ -4188,7 +4188,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C28">
         <v>408787.00040000002</v>
@@ -4205,7 +4205,7 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C29">
         <v>408786.40159999899</v>
@@ -4222,7 +4222,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C30">
         <v>408802.449499999</v>
@@ -4239,7 +4239,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C31">
         <v>408801.83819999901</v>
@@ -4256,7 +4256,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C32">
         <v>408801.21379999898</v>
@@ -4273,7 +4273,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C33">
         <v>408800.62819999899</v>
@@ -4290,7 +4290,7 @@
         <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C34">
         <v>408816.59179999901</v>
@@ -4307,7 +4307,7 @@
         <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C35">
         <v>408815.986199999</v>
@@ -4324,7 +4324,7 @@
         <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C36">
         <v>408815.39</v>
@@ -4341,7 +4341,7 @@
         <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C37">
         <v>408814.777</v>
@@ -4358,7 +4358,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C38">
         <v>408830.81489999901</v>
@@ -4375,7 +4375,7 @@
         <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C39">
         <v>408830.206899999</v>
@@ -4392,7 +4392,7 @@
         <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C40">
         <v>408829.59519999899</v>
@@ -4409,7 +4409,7 @@
         <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C41">
         <v>408828.99920000002</v>
@@ -4426,7 +4426,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C42">
         <v>408845.03460000001</v>
@@ -4443,7 +4443,7 @@
         <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C43">
         <v>408844.4375</v>
@@ -4460,7 +4460,7 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C44">
         <v>408843.829399999</v>
@@ -4477,7 +4477,7 @@
         <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C45">
         <v>408843.20490000001</v>
@@ -4494,7 +4494,7 @@
         <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C46">
         <v>408859.25290000002</v>
@@ -4511,7 +4511,7 @@
         <v>18</v>
       </c>
       <c r="B47" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C47">
         <v>408858.64659999899</v>
@@ -4528,7 +4528,7 @@
         <v>19</v>
       </c>
       <c r="B48" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C48">
         <v>408858.0344</v>
@@ -4545,7 +4545,7 @@
         <v>20</v>
       </c>
       <c r="B49" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C49">
         <v>408857.44079999899</v>
@@ -4575,211 +4575,211 @@
         <v>295</v>
       </c>
       <c r="C1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D1" t="s">
         <v>339</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>340</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>341</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>342</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>343</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>344</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>345</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>346</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>347</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>348</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>349</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>350</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>351</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>352</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>353</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>354</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>355</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>356</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>357</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>358</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>359</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>360</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>361</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>362</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>363</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>364</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>365</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>366</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>367</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>368</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>369</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>370</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>371</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>372</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>373</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>374</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>375</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>376</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>377</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>378</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>379</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>380</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>381</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>382</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>383</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>384</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>385</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>386</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>387</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>388</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>389</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>390</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>391</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>392</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>393</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>394</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>395</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>396</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>397</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>398</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>399</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>400</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>401</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>402</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>403</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>404</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>405</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>406</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
@@ -65508,211 +65508,211 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D1" t="s">
         <v>339</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>340</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>341</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>342</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>343</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>344</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>345</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>346</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>347</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>348</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>349</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>350</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>351</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>352</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>353</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>354</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>355</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>356</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>357</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>358</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>359</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>360</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>361</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>362</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>363</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>364</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>365</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>366</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>367</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>368</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>369</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>370</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>371</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>372</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>373</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>374</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>375</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>376</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>377</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>378</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>379</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>380</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>381</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>382</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>383</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>384</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>385</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>386</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>387</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>388</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>389</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>390</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>391</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>392</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>393</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>394</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>395</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>396</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>397</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>398</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>399</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>400</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>401</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>402</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>403</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>404</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>405</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>406</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">

--- a/Data/2022_F013B4_CO_ISSWC/2022_F013B4_CO_ISSWC_SoilAnalysis.xlsx
+++ b/Data/2022_F013B4_CO_ISSWC/2022_F013B4_CO_ISSWC_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2022_F013B4_CO_ISSWC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87518182-2B24-4CBE-8556-EB31D7DD0FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F21821E-56B7-4D78-AD9E-869414D1F0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1350" yWindow="-24585" windowWidth="17775" windowHeight="24285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1815" yWindow="-25290" windowWidth="16335" windowHeight="23370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="5" r:id="rId1"/>
@@ -1053,12 +1053,6 @@
     <t>p01-1</t>
   </si>
   <si>
-    <t>2015d118EM38</t>
-  </si>
-  <si>
-    <t>2015d119EM38</t>
-  </si>
-  <si>
     <t>SLSND015</t>
   </si>
   <si>
@@ -1627,6 +1621,12 @@
   </si>
   <si>
     <t>2013d260EM38V</t>
+  </si>
+  <si>
+    <t>2015d118EM38V</t>
+  </si>
+  <si>
+    <t>2015d119EM38V</t>
   </si>
 </sst>
 </file>
@@ -2475,13 +2475,13 @@
         <v>296</v>
       </c>
       <c r="B1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -2492,7 +2492,7 @@
         <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C2">
         <v>408706.2476</v>
@@ -2509,7 +2509,7 @@
         <v>116</v>
       </c>
       <c r="B3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C3">
         <v>408705.94109999901</v>
@@ -2526,7 +2526,7 @@
         <v>129</v>
       </c>
       <c r="B4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C4">
         <v>408699.85230000003</v>
@@ -2543,7 +2543,7 @@
         <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C5">
         <v>408700.13030000002</v>
@@ -2560,7 +2560,7 @@
         <v>117</v>
       </c>
       <c r="B6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C6">
         <v>408705.62539999897</v>
@@ -2577,7 +2577,7 @@
         <v>118</v>
       </c>
       <c r="B7" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C7">
         <v>408705.38500000001</v>
@@ -2594,7 +2594,7 @@
         <v>127</v>
       </c>
       <c r="B8" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C8">
         <v>408699.26530000003</v>
@@ -2611,7 +2611,7 @@
         <v>128</v>
       </c>
       <c r="B9" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C9">
         <v>408699.535299999</v>
@@ -2628,7 +2628,7 @@
         <v>119</v>
       </c>
       <c r="B10" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C10">
         <v>408704.99829999899</v>
@@ -2645,7 +2645,7 @@
         <v>126</v>
       </c>
       <c r="B11" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C11">
         <v>408698.93699999899</v>
@@ -2662,7 +2662,7 @@
         <v>121</v>
       </c>
       <c r="B12" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C12">
         <v>408704.38349999901</v>
@@ -2679,7 +2679,7 @@
         <v>124</v>
       </c>
       <c r="B13" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C13">
         <v>408698.26829999901</v>
@@ -2696,7 +2696,7 @@
         <v>99</v>
       </c>
       <c r="B14" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C14">
         <v>408720.46580000001</v>
@@ -2713,7 +2713,7 @@
         <v>100</v>
       </c>
       <c r="B15" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C15">
         <v>408720.19679999899</v>
@@ -2730,7 +2730,7 @@
         <v>113</v>
       </c>
       <c r="B16" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C16">
         <v>408714.09700000001</v>
@@ -2747,7 +2747,7 @@
         <v>114</v>
       </c>
       <c r="B17" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C17">
         <v>408714.40309999901</v>
@@ -2764,7 +2764,7 @@
         <v>101</v>
       </c>
       <c r="B18" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C18">
         <v>408719.8885</v>
@@ -2781,7 +2781,7 @@
         <v>102</v>
       </c>
       <c r="B19" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C19">
         <v>408719.60830000002</v>
@@ -2798,7 +2798,7 @@
         <v>111</v>
       </c>
       <c r="B20" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C20">
         <v>408713.53340000001</v>
@@ -2815,7 +2815,7 @@
         <v>112</v>
       </c>
       <c r="B21" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C21">
         <v>408713.790299999</v>
@@ -2832,7 +2832,7 @@
         <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C22">
         <v>408719.22999999899</v>
@@ -2849,7 +2849,7 @@
         <v>110</v>
       </c>
       <c r="B23" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C23">
         <v>408713.13880000002</v>
@@ -2866,7 +2866,7 @@
         <v>105</v>
       </c>
       <c r="B24" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C24">
         <v>408718.61729999899</v>
@@ -2883,7 +2883,7 @@
         <v>108</v>
       </c>
       <c r="B25" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C25">
         <v>408712.455599999</v>
@@ -2900,7 +2900,7 @@
         <v>83</v>
       </c>
       <c r="B26" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C26">
         <v>408734.69020000001</v>
@@ -2917,7 +2917,7 @@
         <v>84</v>
       </c>
       <c r="B27" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C27">
         <v>408734.44760000001</v>
@@ -2934,7 +2934,7 @@
         <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C28">
         <v>408728.347899999</v>
@@ -2951,7 +2951,7 @@
         <v>98</v>
       </c>
       <c r="B29" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C29">
         <v>408728.57990000001</v>
@@ -2968,7 +2968,7 @@
         <v>85</v>
       </c>
       <c r="B30" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C30">
         <v>408734.16200000001</v>
@@ -2985,7 +2985,7 @@
         <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C31">
         <v>408733.81439999898</v>
@@ -3002,7 +3002,7 @@
         <v>95</v>
       </c>
       <c r="B32" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C32">
         <v>408727.74089999998</v>
@@ -3019,7 +3019,7 @@
         <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C33">
         <v>408727.98920000001</v>
@@ -3036,7 +3036,7 @@
         <v>87</v>
       </c>
       <c r="B34" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C34">
         <v>408733.443499999</v>
@@ -3053,7 +3053,7 @@
         <v>94</v>
       </c>
       <c r="B35" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C35">
         <v>408727.3763</v>
@@ -3070,7 +3070,7 @@
         <v>89</v>
       </c>
       <c r="B36" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C36">
         <v>408732.84250000003</v>
@@ -3087,7 +3087,7 @@
         <v>92</v>
       </c>
       <c r="B37" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C37">
         <v>408726.75140000001</v>
@@ -3104,7 +3104,7 @@
         <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C38">
         <v>408748.9094</v>
@@ -3121,7 +3121,7 @@
         <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C39">
         <v>408748.6594</v>
@@ -3138,7 +3138,7 @@
         <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C40">
         <v>408742.57679999899</v>
@@ -3155,7 +3155,7 @@
         <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C41">
         <v>408742.84710000001</v>
@@ -3172,7 +3172,7 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C42">
         <v>408748.33390000003</v>
@@ -3189,7 +3189,7 @@
         <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C43">
         <v>408747.98800000001</v>
@@ -3206,7 +3206,7 @@
         <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C44">
         <v>408741.9215</v>
@@ -3223,7 +3223,7 @@
         <v>80</v>
       </c>
       <c r="B45" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C45">
         <v>408742.204399999</v>
@@ -3240,7 +3240,7 @@
         <v>71</v>
       </c>
       <c r="B46" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C46">
         <v>408747.652899999</v>
@@ -3257,7 +3257,7 @@
         <v>78</v>
       </c>
       <c r="B47" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C47">
         <v>408741.583099999</v>
@@ -3274,7 +3274,7 @@
         <v>73</v>
       </c>
       <c r="B48" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C48">
         <v>408747.01990000001</v>
@@ -3291,7 +3291,7 @@
         <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C49">
         <v>408740.96580000001</v>
@@ -3308,7 +3308,7 @@
         <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C50">
         <v>408760.11839999899</v>
@@ -3325,7 +3325,7 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C51">
         <v>408759.24219999899</v>
@@ -3342,7 +3342,7 @@
         <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C52">
         <v>408758.807399999</v>
@@ -3359,7 +3359,7 @@
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C53">
         <v>408758.367499999</v>
@@ -3376,7 +3376,7 @@
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C54">
         <v>408788.581799999</v>
@@ -3393,7 +3393,7 @@
         <v>166</v>
       </c>
       <c r="B55" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C55">
         <v>408793.35800000001</v>
@@ -3410,7 +3410,7 @@
         <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C56">
         <v>408787.67560000002</v>
@@ -3427,7 +3427,7 @@
         <v>167</v>
       </c>
       <c r="B57" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C57">
         <v>408792.866099999</v>
@@ -3444,7 +3444,7 @@
         <v>52</v>
       </c>
       <c r="B58" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C58">
         <v>408787.222799999</v>
@@ -3461,7 +3461,7 @@
         <v>168</v>
       </c>
       <c r="B59" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C59">
         <v>408792.38530000002</v>
@@ -3478,7 +3478,7 @@
         <v>53</v>
       </c>
       <c r="B60" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C60">
         <v>408786.80749999901</v>
@@ -3495,7 +3495,7 @@
         <v>170</v>
       </c>
       <c r="B61" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C61">
         <v>408791.43050000002</v>
@@ -3512,7 +3512,7 @@
         <v>48</v>
       </c>
       <c r="B62" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C62">
         <v>408817.00829999999</v>
@@ -3529,7 +3529,7 @@
         <v>46</v>
       </c>
       <c r="B63" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C63">
         <v>408816.12689999898</v>
@@ -3546,7 +3546,7 @@
         <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C64">
         <v>408815.666399999</v>
@@ -3563,7 +3563,7 @@
         <v>44</v>
       </c>
       <c r="B65" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C65">
         <v>408815.248499999</v>
@@ -3580,7 +3580,7 @@
         <v>37</v>
       </c>
       <c r="B66" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C66">
         <v>408845.46089999902</v>
@@ -3597,7 +3597,7 @@
         <v>156</v>
       </c>
       <c r="B67" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C67">
         <v>408850.18070000003</v>
@@ -3614,7 +3614,7 @@
         <v>39</v>
       </c>
       <c r="B68" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C68">
         <v>408844.56319999899</v>
@@ -3631,7 +3631,7 @@
         <v>157</v>
       </c>
       <c r="B69" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C69">
         <v>408849.70020000002</v>
@@ -3648,7 +3648,7 @@
         <v>40</v>
       </c>
       <c r="B70" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C70">
         <v>408844.13500000001</v>
@@ -3665,7 +3665,7 @@
         <v>158</v>
       </c>
       <c r="B71" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C71">
         <v>408849.219199999</v>
@@ -3682,7 +3682,7 @@
         <v>41</v>
       </c>
       <c r="B72" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C72">
         <v>408843.68329999998</v>
@@ -3699,7 +3699,7 @@
         <v>160</v>
       </c>
       <c r="B73" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C73">
         <v>408848.231299999</v>
@@ -3729,13 +3729,13 @@
         <v>296</v>
       </c>
       <c r="B1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -3746,7 +3746,7 @@
         <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C2">
         <v>408702.95299999899</v>
@@ -3763,7 +3763,7 @@
         <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C3">
         <v>408702.35950000002</v>
@@ -3780,7 +3780,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C4">
         <v>408701.76500000001</v>
@@ -3797,7 +3797,7 @@
         <v>64</v>
       </c>
       <c r="B5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C5">
         <v>408701.14669999899</v>
@@ -3814,7 +3814,7 @@
         <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C6">
         <v>408717.2047</v>
@@ -3831,7 +3831,7 @@
         <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C7">
         <v>408716.59240000002</v>
@@ -3848,7 +3848,7 @@
         <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C8">
         <v>408715.98029999901</v>
@@ -3865,7 +3865,7 @@
         <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C9">
         <v>408715.38030000002</v>
@@ -3882,7 +3882,7 @@
         <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C10">
         <v>408731.41739999899</v>
@@ -3899,7 +3899,7 @@
         <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C11">
         <v>408730.80660000001</v>
@@ -3916,7 +3916,7 @@
         <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C12">
         <v>408730.19</v>
@@ -3933,7 +3933,7 @@
         <v>56</v>
       </c>
       <c r="B13" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C13">
         <v>408729.61050000001</v>
@@ -3950,7 +3950,7 @@
         <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C14">
         <v>408745.63719999901</v>
@@ -3967,7 +3967,7 @@
         <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C15">
         <v>408745.02610000002</v>
@@ -3984,7 +3984,7 @@
         <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C16">
         <v>408744.41419999901</v>
@@ -4001,7 +4001,7 @@
         <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C17">
         <v>408743.81449999899</v>
@@ -4018,7 +4018,7 @@
         <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C18">
         <v>408759.7758</v>
@@ -4035,7 +4035,7 @@
         <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C19">
         <v>408759.1692</v>
@@ -4052,7 +4052,7 @@
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C20">
         <v>408758.57179999899</v>
@@ -4069,7 +4069,7 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C21">
         <v>408757.959299999</v>
@@ -4086,7 +4086,7 @@
         <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C22">
         <v>408773.99790000002</v>
@@ -4103,7 +4103,7 @@
         <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C23">
         <v>408773.39649999898</v>
@@ -4120,7 +4120,7 @@
         <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C24">
         <v>408772.784099999</v>
@@ -4137,7 +4137,7 @@
         <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C25">
         <v>408772.17050000001</v>
@@ -4154,7 +4154,7 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C26">
         <v>408788.22350000002</v>
@@ -4171,7 +4171,7 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C27">
         <v>408787.60700000002</v>
@@ -4188,7 +4188,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C28">
         <v>408787.00040000002</v>
@@ -4205,7 +4205,7 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C29">
         <v>408786.40159999899</v>
@@ -4222,7 +4222,7 @@
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C30">
         <v>408802.449499999</v>
@@ -4239,7 +4239,7 @@
         <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C31">
         <v>408801.83819999901</v>
@@ -4256,7 +4256,7 @@
         <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C32">
         <v>408801.21379999898</v>
@@ -4273,7 +4273,7 @@
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C33">
         <v>408800.62819999899</v>
@@ -4290,7 +4290,7 @@
         <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C34">
         <v>408816.59179999901</v>
@@ -4307,7 +4307,7 @@
         <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C35">
         <v>408815.986199999</v>
@@ -4324,7 +4324,7 @@
         <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C36">
         <v>408815.39</v>
@@ -4341,7 +4341,7 @@
         <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C37">
         <v>408814.777</v>
@@ -4358,7 +4358,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C38">
         <v>408830.81489999901</v>
@@ -4375,7 +4375,7 @@
         <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C39">
         <v>408830.206899999</v>
@@ -4392,7 +4392,7 @@
         <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C40">
         <v>408829.59519999899</v>
@@ -4409,7 +4409,7 @@
         <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C41">
         <v>408828.99920000002</v>
@@ -4426,7 +4426,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C42">
         <v>408845.03460000001</v>
@@ -4443,7 +4443,7 @@
         <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C43">
         <v>408844.4375</v>
@@ -4460,7 +4460,7 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C44">
         <v>408843.829399999</v>
@@ -4477,7 +4477,7 @@
         <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C45">
         <v>408843.20490000001</v>
@@ -4494,7 +4494,7 @@
         <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C46">
         <v>408859.25290000002</v>
@@ -4511,7 +4511,7 @@
         <v>18</v>
       </c>
       <c r="B47" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C47">
         <v>408858.64659999899</v>
@@ -4528,7 +4528,7 @@
         <v>19</v>
       </c>
       <c r="B48" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C48">
         <v>408858.0344</v>
@@ -4545,7 +4545,7 @@
         <v>20</v>
       </c>
       <c r="B49" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C49">
         <v>408857.44079999899</v>
@@ -4575,211 +4575,211 @@
         <v>295</v>
       </c>
       <c r="C1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E1" t="s">
         <v>530</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>339</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>340</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>341</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>342</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>343</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>344</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>345</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>346</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>347</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>348</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>349</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>350</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>351</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>352</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>353</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>354</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>355</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>356</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>357</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>358</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>359</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>360</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>361</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>362</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>363</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>364</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>365</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>366</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>367</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>368</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>369</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>370</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>371</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>372</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>373</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>374</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>375</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>376</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>377</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>378</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>379</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>380</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>381</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>382</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>383</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>384</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>385</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>386</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>387</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>388</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>389</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>390</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>391</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>392</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>393</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>394</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>395</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>396</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>397</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>398</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>399</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>400</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>401</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>402</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>403</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>404</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>405</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
@@ -65508,211 +65508,211 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E1" t="s">
         <v>530</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>339</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>340</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>341</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>342</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>343</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>344</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>345</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>346</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>347</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>348</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>349</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>350</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>351</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>352</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>353</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>354</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>355</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>356</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>357</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>358</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>359</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>360</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>361</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>362</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>363</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>364</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>365</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>366</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>367</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>368</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>369</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>370</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>371</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>372</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>373</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>374</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>375</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>376</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>377</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>378</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>379</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>380</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>381</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>382</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>383</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>384</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>385</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>386</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>387</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>388</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>389</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>390</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>391</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>392</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>393</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>394</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>395</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>396</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>397</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>398</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>399</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>400</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>401</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>402</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>403</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>404</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>405</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
